--- a/CSL AU.xlsx
+++ b/CSL AU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BFB77E-C1B0-4AAD-8EB0-B0ABFB90FAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20727CEB-8C4C-4828-88FC-DDA406C7FCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22130" yWindow="1220" windowWidth="16450" windowHeight="18170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13160" yWindow="4120" windowWidth="19050" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -531,9 +531,6 @@
     <t>Atopic Dermatitis</t>
   </si>
   <si>
-    <t>Q224</t>
-  </si>
-  <si>
     <t>1H24</t>
   </si>
   <si>
@@ -592,6 +589,9 @@
   </si>
   <si>
     <t>Haemate</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="19">
-        <v>307</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -1274,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="4">
-        <v>485.19930699999998</v>
+        <v>483.57499999999999</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="J4" s="4">
         <f>J3*J2</f>
-        <v>148956.18724899998</v>
+        <v>61897.599999999999</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -1320,11 +1320,11 @@
         <v>45</v>
       </c>
       <c r="J5" s="4">
-        <f>163+1657</f>
-        <v>1820</v>
+        <f>1145+158</f>
+        <v>1303</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -1346,11 +1346,10 @@
         <v>46</v>
       </c>
       <c r="J6" s="4">
-        <f>11239+944</f>
-        <v>12183</v>
+        <v>10421</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -1371,7 +1370,7 @@
       </c>
       <c r="J7" s="4">
         <f>J4-J5+J6</f>
-        <v>159319.18724899998</v>
+        <v>71015.600000000006</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
@@ -1392,7 +1391,7 @@
       </c>
       <c r="J8" s="4">
         <f>J7/1.5</f>
-        <v>106212.79149933333</v>
+        <v>47343.733333333337</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
@@ -1973,13 +1972,13 @@
         <v>97</v>
       </c>
       <c r="AG2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH2" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AH2" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AI2" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
@@ -2095,7 +2094,7 @@
     </row>
     <row r="3" spans="1:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -2140,7 +2139,7 @@
     </row>
     <row r="4" spans="1:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -2185,7 +2184,7 @@
     </row>
     <row r="5" spans="1:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -2230,7 +2229,7 @@
     </row>
     <row r="6" spans="1:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
@@ -2970,7 +2969,7 @@
     </row>
     <row r="24" spans="2:35" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -3005,7 +3004,7 @@
     </row>
     <row r="25" spans="2:35" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -3040,7 +3039,7 @@
     </row>
     <row r="26" spans="2:35" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -3075,7 +3074,7 @@
     </row>
     <row r="27" spans="2:35" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -3180,7 +3179,7 @@
     </row>
     <row r="30" spans="2:35" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -3215,7 +3214,7 @@
     </row>
     <row r="31" spans="2:35" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -3250,7 +3249,7 @@
     </row>
     <row r="32" spans="2:35" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -3285,7 +3284,7 @@
     </row>
     <row r="33" spans="2:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -3320,7 +3319,7 @@
     </row>
     <row r="34" spans="2:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
@@ -3355,7 +3354,7 @@
     </row>
     <row r="35" spans="2:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -3390,7 +3389,7 @@
     </row>
     <row r="36" spans="2:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -3425,7 +3424,7 @@
     </row>
     <row r="37" spans="2:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
@@ -3460,7 +3459,7 @@
     </row>
     <row r="38" spans="2:68" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
@@ -3731,7 +3730,7 @@
     </row>
     <row r="45" spans="2:68" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -3845,7 +3844,7 @@
         <v>12622</v>
       </c>
       <c r="BF46" s="7">
-        <f t="shared" ref="BE46:BP46" si="10">SUM(BF10:BF44)</f>
+        <f t="shared" ref="BF46:BP46" si="10">SUM(BF10:BF44)</f>
         <v>0</v>
       </c>
       <c r="BG46" s="7">
@@ -5141,18 +5140,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5172,18 +5171,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E77DD1E9-4570-4C5D-AEC3-37D82CF0539A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{212CB4BB-6234-4E6B-8AF1-174BA7056159}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E77DD1E9-4570-4C5D-AEC3-37D82CF0539A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>